--- a/tests/fixtures/charts/pie-explicit-points.xlsx
+++ b/tests/fixtures/charts/pie-explicit-points.xlsx
@@ -1369,7 +1369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D5388EEC-07DD-D838-1C38-92371EB43CE8}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E1AB46C8-91B6-779F-E348-D0BE2CB5CD15}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <sheetData>
